--- a/Immigration_Networks/MigrationData/Matrices/DifferenceMatrices_2010.xlsx
+++ b/Immigration_Networks/MigrationData/Matrices/DifferenceMatrices_2010.xlsx
@@ -9,10 +9,10 @@
     <sheet name="RawMatrix" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="DiffMat" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DiffMat_Pos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DiffMat_PopScaled" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DiffMat_PopScaled_Per1000" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DiffMat_PopScaled_Pos" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DiffMat_PopScaled_Per1000_Pos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DiffMat_PopScaled_dest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DiffMat_PopScaled_org" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DiffMat_PopScaled_Per1000_dest" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DiffMat_PopScaled_Per1000_org" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="DM_10000_binary" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
@@ -4230,16 +4230,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0320624571255443</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0000705823889526944</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0.000536364438669262</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.00750820768241868</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0000371616718982588</v>
@@ -4269,16 +4269,16 @@
         <v>0.000592809998669921</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0834770830051977</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.00540989923413097</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.000575251911761256</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0262936962101947</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0.000288064252270205</v>
@@ -4304,7 +4304,7 @@
         <v>0.00122690359797046</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0000391046198881318</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0.0000526782384660448</v>
@@ -4313,34 +4313,34 @@
         <v>0.0000230156558195053</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.00000955794661689064</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.000000275859938185305</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0000115585527697648</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0000551022855982975</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00000601167983510821</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0.0000863230012922025</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.000416916049771618</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.000091654734928316</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0.000248408201890903</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.000130191885559843</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0.0000432131059870787</v>
@@ -4354,7 +4354,7 @@
         <v>0.00033561751329159</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.00161239871562003</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4363,10 +4363,10 @@
         <v>0.000624208663604518</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.000304688820463728</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0000943111420831413</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0.0000335823770221036</v>
@@ -4378,7 +4378,7 @@
         <v>0.000000823960915249193</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.00000558616374825243</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0.00000534427708709556</v>
@@ -4387,7 +4387,7 @@
         <v>0.0000166998203202595</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.000043112332531776</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0.000350283471229924</v>
@@ -4396,13 +4396,13 @@
         <v>0.00576578988817137</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.000299176187295092</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.00106560960531627</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.00353484375782045</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0.0000986340878228346</v>
@@ -4413,61 +4413,61 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.000457211558882527</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.000335875478585729</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000111902233703522</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00146640588950976</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.00132928908337029</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.000593947138704655</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.000781670039864177</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.00715527658802399</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.00103033686912211</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.000690530313858208</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.00052952495295876</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.00149622122981793</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.000264254085588375</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.000751771932587809</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.000847832092102381</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.00195732215525195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.00187571650225348</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.000517516827880569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4478,7 +4478,7 @@
         <v>0.00321563654557648</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.00207025002590268</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0.0000274434645103502</v>
@@ -4490,13 +4490,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.000269265792113766</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0.000376429912371945</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.000597412138231366</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0.0000362542802709645</v>
@@ -4517,16 +4517,16 @@
         <v>0.000454810642862659</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0000373287131831785</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.00402758074971303</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.000276955183879302</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.000962883693659983</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0.000243741339387792</v>
@@ -4537,7 +4537,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.0000414785756177366</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0.000171964316667722</v>
@@ -4588,7 +4588,7 @@
         <v>0.00207366621920218</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.000129893963624923</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0.0306671552129104</v>
@@ -4599,61 +4599,61 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0000330283129167675</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0000235702090235599</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.000000802072601735164</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0.0000791299842459395</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0000998168724155287</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.000443505794607886</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0000340260271913723</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.00211939226620397</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.000111240520073224</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.000404673632455422</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.00000510074469270185</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0477574716592236</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.00136002769382817</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0000130729248700583</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.000117173614221678</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.000252772195287386</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0000923557998250602</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.00000839291464596553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4661,13 +4661,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0000826081728348433</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.000034078593879897</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.00000199731804745815</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0.000344621901085882</v>
@@ -4676,7 +4676,7 @@
         <v>0.000524227737519923</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.00464134542403813</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0.000112599734721171</v>
@@ -4685,34 +4685,34 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0000486136939997024</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0000135171369710799</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.00000546856260074894</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0.00000371206027374637</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0000357265544486431</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0.0004462957889937</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.000030240982831942</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.000189637601649056</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.00133841091399966</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.000225824826669018</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0.0009624106670477</v>
@@ -4723,22 +4723,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.00000334022183460139</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0.00000569613384736031</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0000000262115229325217</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0.00126970580781918</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0000128044967530124</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00000285859014601991</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0.00282289510379918</v>
@@ -4753,28 +4753,28 @@
         <v>0.000563443923743486</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.00060837758933332</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0.0000642889671390799</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.000899175541051185</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0.000682069156468661</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.00000173255630808001</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.00000416143449393105</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.00383788005036591</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0000214503793142075</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0.0000258723732474805</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.00000962183304594131</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0.000000392836817059332</v>
@@ -4797,10 +4797,10 @@
         <v>0.000436881731202637</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0000152489915876784</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0000114120278485639</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0.000354041661023876</v>
@@ -4809,34 +4809,34 @@
         <v>0.0000130001975234093</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.00134635213551718</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.000498633480777381</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0.000157063768513144</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.00099776709034696</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0.000326206987876316</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0000080327610647346</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.00000828847696725109</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.00261833461872334</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.000036346476060185</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0.00000610393792433857</v>
@@ -4847,22 +4847,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.00000174489200314998</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0.00000913345599662946</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.000000225419097219687</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0.000162470876744435</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0000128626990109807</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.00000522586011069265</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0.000714668101856008</v>
@@ -4889,16 +4889,16 @@
         <v>0.00029361565065375</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.00000393762797290912</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.00000398947439087604</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.00157421525644398</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0000143002528761384</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0.00000762992240542321</v>
@@ -4909,43 +4909,43 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.000317296147258515</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0.000607914974399316</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.00000983456340428214</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0.0017394852597449</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.000108547211110764</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.000226386939923468</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0.000125769294337682</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0000276585835064372</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.00119012914598593</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.00121681818733538</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.00110191536405091</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.00047887323943662</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0.00069293293554285</v>
@@ -4954,16 +4954,16 @@
         <v>0.000179240825326823</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.000136192401619562</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.0369375254164228</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.000552943111210683</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.000248353974296525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4971,7 +4971,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.00000398832457862852</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0.00000343732214926915</v>
@@ -4983,10 +4983,10 @@
         <v>0.00025473070686119</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.00000680966418228388</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.00000926808523904893</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0.061028617233554</v>
@@ -5001,7 +5001,7 @@
         <v>0.000400617595229609</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.000746210223974924</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0.00002481828307723</v>
@@ -5016,13 +5016,13 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.00000199473719543802</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.000810678041444548</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0000107251896571038</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0.0000639526223436382</v>
@@ -5033,61 +5033,61 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0000503276707765687</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0000288735060538609</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00000625406937169968</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0.0000263181765784721</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0000901552975928012</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.00100769769194305</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0.00101669000239466</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.000100817858344807</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.000382812241224775</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0000766200978309685</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.000124285513653385</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0000210083027483008</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.00183029886636895</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.0000163805323673019</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.000114731780758297</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.000308864057076844</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.000193649257697707</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.000262018471695329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5101,7 +5101,7 @@
         <v>0.000259959763689013</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.000191905043998164</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0.000139574063121164</v>
@@ -5128,7 +5128,7 @@
         <v>0.00000310713784133463</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0000101302747998162</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
         <v>0.0000959464355563002</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.000596439713708937</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0.00000752587800898562</v>
@@ -5172,7 +5172,7 @@
         <v>0.00681595002614445</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0000419632100341517</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0.000747811493557561</v>
@@ -5199,7 +5199,7 @@
         <v>0.00097950181058091</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.0000823751771932588</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>0.00134440089900979</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.000148663045524855</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0.00140883049069592</v>
@@ -5219,61 +5219,61 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.00443586445040788</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.00754688630173108</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.00172810473772281</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0177061966263724</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.00498653665368679</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.014326181840547</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0171632285702182</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0274620550102032</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.195649024949372</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0558603271478179</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0605249322954664</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.101717679781088</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0430750601167984</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0280540945730138</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.00467490943455662</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.0143032974519089</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0152452612537032</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0058978259749957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5343,58 +5343,58 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.000207043899688053</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.000122368668513982</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0000149091142440183</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0.000436355367671068</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.000409045469000779</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0197477660453</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0.0000531172237865952</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.00184058919017657</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.00012293496855518</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0000121378372801534</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0000273428130037447</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0.0000637459559239755</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.000316729646169701</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0.00221826624068908</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0000341786108048512</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.00139707266126006</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.000549724166685682</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.00123190720089234</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -5481,58 +5481,58 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-32.0624571255443</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0705823889526944</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.536364438669262</v>
+        <v>0.000457211558882527</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.50820768241868</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0371616718982588</v>
+        <v>0.0000414785756177366</v>
       </c>
       <c r="H2" t="n">
-        <v>0.290827774864622</v>
+        <v>0.0000330283129167675</v>
       </c>
       <c r="I2" t="n">
-        <v>0.219809462207033</v>
+        <v>0.0000826081728348433</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0220821525286784</v>
+        <v>0.00000334022183460139</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0266204840348819</v>
+        <v>0.00000962183304594131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00869998595573696</v>
+        <v>0.00000174489200314998</v>
       </c>
       <c r="M2" t="n">
-        <v>0.113311307492848</v>
+        <v>0.000317296147258515</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0274819649604947</v>
+        <v>0.00000398832457862852</v>
       </c>
       <c r="O2" t="n">
-        <v>0.592809998669921</v>
+        <v>0.0000503276707765687</v>
       </c>
       <c r="P2" t="n">
-        <v>-83.4770830051977</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.40989923413097</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.575251911761256</v>
+        <v>0.00443586445040788</v>
       </c>
       <c r="S2" t="n">
-        <v>-26.2936962101947</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.288064252270205</v>
+        <v>0.000207043899688053</v>
       </c>
     </row>
     <row r="3">
@@ -5540,61 +5540,61 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>8.13795195943395</v>
+        <v>0.0320624571255443</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0860681567012282</v>
+        <v>0.00161239871562003</v>
       </c>
       <c r="E3" t="n">
-        <v>0.100009070998194</v>
+        <v>0.000335875478585729</v>
       </c>
       <c r="F3" t="n">
-        <v>1.22690359797046</v>
+        <v>0.00207025002590268</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0391046198881318</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0526782384660448</v>
+        <v>0.0000235702090235599</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0230156558195053</v>
+        <v>0.000034078593879897</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.00955794661689064</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.000275859938185305</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0115585527697648</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0551022855982975</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00601167983510821</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0863230012922025</v>
+        <v>0.0000288735060538609</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.416916049771618</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.091654734928316</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.248408201890903</v>
+        <v>0.00754688630173108</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.130191885559843</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0432131059870787</v>
+        <v>0.000122368668513982</v>
       </c>
     </row>
     <row r="4">
@@ -5602,61 +5602,61 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.33561751329159</v>
+        <v>0.0000705823889526944</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.61239871562003</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.624208663604518</v>
+        <v>0.000111902233703522</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.304688820463728</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0943111420831413</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0335823770221036</v>
+        <v>0.000000802072601735164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0252707921245865</v>
+        <v>0.00000199731804745815</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000823960915249193</v>
+        <v>0.0000000262115229325217</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.00558616374825243</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00534427708709556</v>
+        <v>0.000000225419097219687</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0166998203202595</v>
+        <v>0.00000983456340428214</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.043112332531776</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.350283471229924</v>
+        <v>0.00000625406937169968</v>
       </c>
       <c r="P4" t="n">
-        <v>5.76578988817137</v>
+        <v>0.000191905043998164</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.299176187295092</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.06560960531627</v>
+        <v>0.00172810473772281</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.53484375782045</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0986340878228346</v>
+        <v>0.0000149091142440183</v>
       </c>
     </row>
     <row r="5">
@@ -5664,61 +5664,61 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.457211558882527</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.335875478585729</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.111902233703522</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.46640588950976</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.32928908337029</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.593947138704655</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.781670039864177</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.15527658802399</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.03033686912211</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.690530313858208</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.52952495295876</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.49622122981793</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.264254085588375</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.751771932587809</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.847832092102381</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95732215525195</v>
+        <v>0.0177061966263724</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.87571650225348</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.517516827880569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5726,61 +5726,61 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3.21563654557648</v>
+        <v>0.00750820768241868</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.07025002590268</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0274434645103502</v>
+        <v>0.000304688820463728</v>
       </c>
       <c r="E6" t="n">
-        <v>0.736762732105117</v>
+        <v>0.00146640588950976</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.269265792113766</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.376429912371945</v>
+        <v>0.0000998168724155287</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.597412138231366</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0362542802709645</v>
+        <v>0.0000128044967530124</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0180688259511375</v>
+        <v>0.0000152489915876784</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0274670985173981</v>
+        <v>0.0000128626990109807</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0166019002650767</v>
+        <v>0.000108547211110764</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0200961868773617</v>
+        <v>0.00000680966418228388</v>
       </c>
       <c r="O6" t="n">
-        <v>0.454810642862659</v>
+        <v>0.0000901552975928012</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0373287131831785</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.02758074971303</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.276955183879302</v>
+        <v>0.00498653665368679</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.962883693659983</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.243741339387792</v>
+        <v>0.000409045469000779</v>
       </c>
     </row>
     <row r="7">
@@ -5788,61 +5788,61 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.0414785756177366</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.171964316667722</v>
+        <v>0.0000391046198881318</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0221382522688078</v>
+        <v>0.0000943111420831413</v>
       </c>
       <c r="E7" t="n">
-        <v>1.74056722922646</v>
+        <v>0.00132928908337029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.70174462432305</v>
+        <v>0.000269265792113766</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.35890474040493</v>
+        <v>0.000443505794607886</v>
       </c>
       <c r="I7" t="n">
-        <v>13.7846533198856</v>
+        <v>0.00464134542403813</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0210933994303793</v>
+        <v>0.00000285859014601991</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0352411071031727</v>
+        <v>0.0000114120278485639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0290828101948921</v>
+        <v>0.00000522586011069265</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0902377817625108</v>
+        <v>0.000226386939923468</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0712813466162831</v>
+        <v>0.00000926808523904893</v>
       </c>
       <c r="O7" t="n">
-        <v>13.2485253887985</v>
+        <v>0.00100769769194305</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0646226067280697</v>
+        <v>0.0000419632100341517</v>
       </c>
       <c r="R7" t="n">
-        <v>2.07366621920218</v>
+        <v>0.014326181840547</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.129893963624923</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>30.6671552129104</v>
+        <v>0.0197477660453</v>
       </c>
     </row>
     <row r="8">
@@ -5850,61 +5850,61 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0330283129167675</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0235702090235599</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.000802072601735164</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0791299842459395</v>
+        <v>0.000593947138704655</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0998168724155287</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.443505794607886</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0340260271913723</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.11939226620397</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.111240520073224</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.404673632455422</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.00510074469270185</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-47.7574716592236</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.36002769382817</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0130729248700583</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.117173614221678</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.252772195287386</v>
+        <v>0.0171632285702182</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0923557998250602</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.00839291464596553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5912,61 +5912,61 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0826081728348433</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.034078593879897</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.00199731804745815</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.344621901085882</v>
+        <v>0.000781670039864177</v>
       </c>
       <c r="F9" t="n">
-        <v>0.524227737519923</v>
+        <v>0.000597412138231366</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.64134542403813</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.112599734721171</v>
+        <v>0.0000340260271913723</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0486136939997024</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0135171369710799</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.00546856260074894</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00371206027374637</v>
+        <v>0.0000276585835064372</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0357265544486431</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4462957889937</v>
+        <v>0.000100817858344807</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.030240982831942</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.189637601649056</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33841091399966</v>
+        <v>0.0274620550102032</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.225824826669018</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9624106670477</v>
+        <v>0.00184058919017657</v>
       </c>
     </row>
     <row r="10">
@@ -5974,61 +5974,61 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.00334022183460139</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00569613384736031</v>
+        <v>0.00000955794661689064</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0000262115229325217</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.26970580781918</v>
+        <v>0.00715527658802399</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0128044967530124</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00285859014601991</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82289510379918</v>
+        <v>0.00211939226620397</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0195666238234987</v>
+        <v>0.0000486136939997024</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.563443923743486</v>
+        <v>0.00134635213551718</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.60837758933332</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0642889671390799</v>
+        <v>0.00119012914598593</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.899175541051185</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.682069156468661</v>
+        <v>0.000382812241224775</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.00173255630808001</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.00416143449393105</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.83788005036591</v>
+        <v>0.195649024949372</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0214503793142075</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0258723732474805</v>
+        <v>0.00012293496855518</v>
       </c>
     </row>
     <row r="11">
@@ -6036,61 +6036,61 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.00962183304594131</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000392836817059332</v>
+        <v>0.000000275859938185305</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000424626671506852</v>
+        <v>0.00000558616374825243</v>
       </c>
       <c r="E11" t="n">
-        <v>0.436881731202637</v>
+        <v>0.00103033686912211</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0152489915876784</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0114120278485639</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.354041661023876</v>
+        <v>0.000111240520073224</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0130001975234093</v>
+        <v>0.0000135171369710799</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.34635213551718</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.498633480777381</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.157063768513144</v>
+        <v>0.00121681818733538</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.99776709034696</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.326206987876316</v>
+        <v>0.0000766200978309685</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0080327610647346</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.00828847696725109</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.61833461872334</v>
+        <v>0.0558603271478179</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.036346476060185</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.00610393792433857</v>
+        <v>0.0000121378372801534</v>
       </c>
     </row>
     <row r="12">
@@ -6098,61 +6098,61 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.00174489200314998</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00913345599662946</v>
+        <v>0.0000115585527697648</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.000225419097219687</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.162470876744435</v>
+        <v>0.000690530313858208</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0128626990109807</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.00522586011069265</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.714668101856008</v>
+        <v>0.000404673632455422</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00291841168892862</v>
+        <v>0.00000546856260074894</v>
       </c>
       <c r="J12" t="n">
-        <v>0.80665773602896</v>
+        <v>0.00060837758933332</v>
       </c>
       <c r="K12" t="n">
-        <v>0.276687517999861</v>
+        <v>0.000498633480777381</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.078923564477303</v>
+        <v>0.00110191536405091</v>
       </c>
       <c r="N12" t="n">
-        <v>1.03126073514256</v>
+        <v>0.000746210223974924</v>
       </c>
       <c r="O12" t="n">
-        <v>0.29361565065375</v>
+        <v>0.000124285513653385</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.00393762797290912</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.00398947439087604</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57421525644398</v>
+        <v>0.0605249322954664</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0143002528761384</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.00762992240542321</v>
+        <v>0.0000273428130037447</v>
       </c>
     </row>
     <row r="13">
@@ -6160,61 +6160,61 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.317296147258515</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.607914974399316</v>
+        <v>0.0000551022855982975</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.00983456340428214</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7394852597449</v>
+        <v>0.00052952495295876</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.108547211110764</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.226386939923468</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.125769294337682</v>
+        <v>0.00000510074469270185</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0276585835064372</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.19012914598593</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.21681818733538</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.10191536405091</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.47887323943662</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.69293293554285</v>
+        <v>0.0000210083027483008</v>
       </c>
       <c r="P13" t="n">
-        <v>0.179240825326823</v>
+        <v>0.0000101302747998162</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.136192401619562</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>36.9375254164228</v>
+        <v>0.101717679781088</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.552943111210683</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.248353974296526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6222,61 +6222,61 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.00398832457862852</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00343732214926915</v>
+        <v>0.00000601167983510821</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00131581845121259</v>
+        <v>0.000043112332531776</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25473070686119</v>
+        <v>0.00149622122981793</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.00680966418228389</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.00926808523904893</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>61.028617233554</v>
+        <v>0.0477574716592236</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0137961279840262</v>
+        <v>0.0000357265544486431</v>
       </c>
       <c r="J14" t="n">
-        <v>0.862687078265905</v>
+        <v>0.000899175541051185</v>
       </c>
       <c r="K14" t="n">
-        <v>0.400617595229609</v>
+        <v>0.00099776709034696</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.746210223974924</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02481828307723</v>
+        <v>0.00047887323943662</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.12876837336636</v>
+        <v>0.00183029886636895</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.00199473719543802</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.810678041444548</v>
+        <v>0.0430750601167984</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0107251896571038</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0639526223436382</v>
+        <v>0.000316729646169701</v>
       </c>
     </row>
     <row r="15">
@@ -6284,61 +6284,61 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0503276707765687</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0288735060538609</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00625406937169968</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0263181765784721</v>
+        <v>0.000264254085588375</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0901552975928012</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.00769769194305</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01669000239467</v>
+        <v>0.00136002769382817</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.100817858344807</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.382812241224775</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0766200978309685</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.124285513653385</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0210083027483008</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.83029886636895</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.0163805323673019</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.114731780758297</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.308864057076844</v>
+        <v>0.0280540945730138</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.193649257697707</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.262018471695329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -6346,61 +6346,61 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>13.2112254585925</v>
+        <v>0.0834770830051977</v>
       </c>
       <c r="C16" t="n">
-        <v>0.259959763689013</v>
+        <v>0.000416916049771618</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.191905043998164</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.139574063121164</v>
+        <v>0.000751771932587809</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0137939351384725</v>
+        <v>0.0000373287131831785</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0182178908028405</v>
+        <v>0.0000130729248700583</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0127348873698703</v>
+        <v>0.000030240982831942</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00181271401354822</v>
+        <v>0.00000173255630808001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00351721421186264</v>
+        <v>0.0000080327610647346</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00310713784133463</v>
+        <v>0.00000393762797290912</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0101302747998162</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.03053602766799</v>
+        <v>0.0000163805323673019</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0179870267795532</v>
+        <v>0.0000823751771932588</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0959464355563002</v>
+        <v>0.00467490943455662</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.596439713708937</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.00752587800898562</v>
+        <v>0.0000341786108048512</v>
       </c>
     </row>
     <row r="17">
@@ -6408,61 +6408,61 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3.92104652839278</v>
+        <v>0.00540989923413097</v>
       </c>
       <c r="C17" t="n">
-        <v>0.26172752936578</v>
+        <v>0.000091654734928316</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0456028075980013</v>
+        <v>0.000299176187295092</v>
       </c>
       <c r="E17" t="n">
-        <v>0.720884098902772</v>
+        <v>0.000847832092102381</v>
       </c>
       <c r="F17" t="n">
-        <v>6.81595002614445</v>
+        <v>0.00402758074971303</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0419632100341517</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.747811493557561</v>
+        <v>0.000117173614221678</v>
       </c>
       <c r="I17" t="n">
-        <v>0.365730046653464</v>
+        <v>0.000189637601649056</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0199398541490305</v>
+        <v>0.00000416143449393105</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0166205612756646</v>
+        <v>0.00000828847696725109</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0144171195837927</v>
+        <v>0.00000398947439087604</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0352512198657929</v>
+        <v>0.000136192401619562</v>
       </c>
       <c r="N17" t="n">
-        <v>0.00996221229817932</v>
+        <v>0.00000199473719543802</v>
       </c>
       <c r="O17" t="n">
-        <v>0.97950181058091</v>
+        <v>0.000114731780758297</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.0823751771932588</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34440089900979</v>
+        <v>0.0143032974519089</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.148663045524855</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.40883049069592</v>
+        <v>0.00139707266126006</v>
       </c>
     </row>
     <row r="18">
@@ -6470,61 +6470,61 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>-4.43586445040788</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-7.54688630173108</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.72810473772281</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-17.7061966263724</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.98653665368679</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.326181840547</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-17.1632285702182</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-27.4620550102032</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-195.649024949372</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-55.8603271478179</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-60.5249322954664</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-101.717679781088</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-43.0750601167984</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-28.0540945730138</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.67490943455662</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-14.3032974519089</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-15.2452612537032</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-5.8978259749957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -6532,61 +6532,61 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2.19998476460011</v>
+        <v>0.0262936962101947</v>
       </c>
       <c r="C19" t="n">
-        <v>0.042917422263732</v>
+        <v>0.000130191885559843</v>
       </c>
       <c r="D19" t="n">
-        <v>0.062199943918874</v>
+        <v>0.00353484375782045</v>
       </c>
       <c r="E19" t="n">
-        <v>0.184110266375623</v>
+        <v>0.00187571650225348</v>
       </c>
       <c r="F19" t="n">
-        <v>0.188109697753346</v>
+        <v>0.000962883693659983</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00973707268488032</v>
+        <v>0.000129893963624923</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0680427246853079</v>
+        <v>0.0000923557998250602</v>
       </c>
       <c r="I19" t="n">
-        <v>0.050276274095634</v>
+        <v>0.000225824826669018</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0118650371795884</v>
+        <v>0.0000214503793142075</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0084137281146518</v>
+        <v>0.000036346476060185</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00596570465536249</v>
+        <v>0.0000143002528761384</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0165217838562908</v>
+        <v>0.000552943111210683</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0061834421161113</v>
+        <v>0.0000107251896571038</v>
       </c>
       <c r="O19" t="n">
-        <v>0.190850172924937</v>
+        <v>0.000193649257697707</v>
       </c>
       <c r="P19" t="n">
-        <v>0.315325248070562</v>
+        <v>0.000596439713708937</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0171616182848892</v>
+        <v>0.000148663045524855</v>
       </c>
       <c r="R19" t="n">
-        <v>0.165417977840605</v>
+        <v>0.0152452612537032</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.143407859756477</v>
+        <v>0.00123190720089234</v>
       </c>
     </row>
     <row r="20">
@@ -6594,58 +6594,58 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.207043899688053</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.122368668513982</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0149091142440183</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.436355367671068</v>
+        <v>0.000517516827880569</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.409045469000779</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-19.7477660453</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0531172237865952</v>
+        <v>0.00000839291464596553</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.84058919017657</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.12293496855518</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0121378372801534</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0273428130037447</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0637459559239755</v>
+        <v>0.000248353974296525</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.316729646169701</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.21826624068908</v>
+        <v>0.000262018471695329</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0341786108048512</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.39707266126006</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.549724166685682</v>
+        <v>0.0058978259749957</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.23190720089234</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -6738,37 +6738,37 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000536364438669262</v>
+        <v>0.536364438669262</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0000371616718982588</v>
+        <v>0.0371616718982588</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000290827774864622</v>
+        <v>0.290827774864622</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000219809462207033</v>
+        <v>0.219809462207033</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0000220821525286784</v>
+        <v>0.0220821525286784</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0000266204840348819</v>
+        <v>0.0266204840348819</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00000869998595573696</v>
+        <v>0.00869998595573696</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000113311307492848</v>
+        <v>0.113311307492848</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0000274819649604947</v>
+        <v>0.0274819649604947</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000592809998669921</v>
+        <v>0.592809998669921</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -6777,13 +6777,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000575251911761256</v>
+        <v>0.575251911761256</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000288064252270205</v>
+        <v>0.288064252270205</v>
       </c>
     </row>
     <row r="3">
@@ -6791,28 +6791,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00813795195943395</v>
+        <v>8.13795195943395</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000860681567012282</v>
+        <v>0.0860681567012282</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000100009070998194</v>
+        <v>0.100009070998194</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00122690359797046</v>
+        <v>1.22690359797046</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0000526782384660448</v>
+        <v>0.0526782384660448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0000230156558195053</v>
+        <v>0.0230156558195053</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -6830,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0000863230012922025</v>
+        <v>0.0863230012922025</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -6839,13 +6839,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000248408201890903</v>
+        <v>0.248408201890903</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0000432131059870787</v>
+        <v>0.0432131059870787</v>
       </c>
     </row>
     <row r="4">
@@ -6853,7 +6853,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00033561751329159</v>
+        <v>0.33561751329159</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000624208663604518</v>
+        <v>0.624208663604518</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -6871,43 +6871,43 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0000335823770221036</v>
+        <v>0.0335823770221036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0000252707921245865</v>
+        <v>0.0252707921245865</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000000823960915249193</v>
+        <v>0.000823960915249193</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00000534427708709556</v>
+        <v>0.00534427708709556</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0000166998203202595</v>
+        <v>0.0166998203202595</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000350283471229924</v>
+        <v>0.350283471229924</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00576578988817137</v>
+        <v>5.76578988817137</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00106560960531627</v>
+        <v>1.06560960531627</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0000986340878228346</v>
+        <v>0.0986340878228346</v>
       </c>
     </row>
     <row r="5">
@@ -6963,7 +6963,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00195732215525195</v>
+        <v>1.95732215525195</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -6977,16 +6977,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00321563654557648</v>
+        <v>3.21563654557648</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000274434645103502</v>
+        <v>0.0274434645103502</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000736762732105117</v>
+        <v>0.736762732105117</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -6995,28 +6995,28 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000376429912371945</v>
+        <v>0.376429912371945</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0000362542802709645</v>
+        <v>0.0362542802709645</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0000180688259511375</v>
+        <v>0.0180688259511375</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0000274670985173981</v>
+        <v>0.0274670985173981</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0000166019002650767</v>
+        <v>0.0166019002650767</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0000200961868773617</v>
+        <v>0.0200961868773617</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000454810642862659</v>
+        <v>0.454810642862659</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -7025,13 +7025,13 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000276955183879302</v>
+        <v>0.276955183879302</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000243741339387792</v>
+        <v>0.243741339387792</v>
       </c>
     </row>
     <row r="7">
@@ -7042,58 +7042,58 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000171964316667722</v>
+        <v>0.171964316667722</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000221382522688078</v>
+        <v>0.0221382522688078</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00174056722922646</v>
+        <v>1.74056722922646</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00070174462432305</v>
+        <v>0.70174462432305</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00435890474040493</v>
+        <v>4.35890474040493</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0137846533198856</v>
+        <v>13.7846533198856</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0000210933994303793</v>
+        <v>0.0210933994303793</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0000352411071031727</v>
+        <v>0.0352411071031727</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0000290828101948921</v>
+        <v>0.0290828101948921</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0000902377817625108</v>
+        <v>0.0902377817625108</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0000712813466162831</v>
+        <v>0.0712813466162831</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0132485253887985</v>
+        <v>13.2485253887985</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0000646226067280697</v>
+        <v>0.0646226067280697</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00207366621920218</v>
+        <v>2.07366621920218</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0306671552129104</v>
+        <v>30.6671552129104</v>
       </c>
     </row>
     <row r="8">
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000791299842459395</v>
+        <v>0.0791299842459395</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.000252772195287386</v>
+        <v>0.252772195287386</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -7172,16 +7172,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000344621901085882</v>
+        <v>0.344621901085882</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000524227737519923</v>
+        <v>0.524227737519923</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000112599734721171</v>
+        <v>0.112599734721171</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -7196,13 +7196,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00000371206027374637</v>
+        <v>0.00371206027374637</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0004462957889937</v>
+        <v>0.4462957889937</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -7211,13 +7211,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00133841091399966</v>
+        <v>1.33841091399966</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0009624106670477</v>
+        <v>0.9624106670477</v>
       </c>
     </row>
     <row r="10">
@@ -7228,13 +7228,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00000569613384736031</v>
+        <v>0.00569613384736031</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00126970580781918</v>
+        <v>1.26970580781918</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -7243,28 +7243,28 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00282289510379918</v>
+        <v>2.82289510379918</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0000195666238234987</v>
+        <v>0.0195666238234987</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.000563443923743486</v>
+        <v>0.563443923743486</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0000642889671390799</v>
+        <v>0.0642889671390799</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.000682069156468661</v>
+        <v>0.682069156468661</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -7273,13 +7273,13 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00383788005036591</v>
+        <v>3.83788005036591</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0000258723732474805</v>
+        <v>0.0258723732474805</v>
       </c>
     </row>
     <row r="11">
@@ -7290,13 +7290,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000000392836817059332</v>
+        <v>0.000392836817059332</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000000424626671506852</v>
+        <v>0.000424626671506852</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000436881731202637</v>
+        <v>0.436881731202637</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -7305,10 +7305,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000354041661023876</v>
+        <v>0.354041661023876</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0000130001975234093</v>
+        <v>0.0130001975234093</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -7320,13 +7320,13 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.000157063768513144</v>
+        <v>0.157063768513144</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.000326206987876316</v>
+        <v>0.326206987876316</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -7335,13 +7335,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00261833461872334</v>
+        <v>2.61833461872334</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.00000610393792433857</v>
+        <v>0.00610393792433857</v>
       </c>
     </row>
     <row r="12">
@@ -7352,13 +7352,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00000913345599662946</v>
+        <v>0.00913345599662946</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000162470876744435</v>
+        <v>0.162470876744435</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -7367,28 +7367,28 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000714668101856008</v>
+        <v>0.714668101856008</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00000291841168892862</v>
+        <v>0.00291841168892862</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00080665773602896</v>
+        <v>0.80665773602896</v>
       </c>
       <c r="K12" t="n">
-        <v>0.000276687517999861</v>
+        <v>0.276687517999861</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.000078923564477303</v>
+        <v>0.078923564477303</v>
       </c>
       <c r="N12" t="n">
-        <v>0.00103126073514256</v>
+        <v>1.03126073514256</v>
       </c>
       <c r="O12" t="n">
-        <v>0.00029361565065375</v>
+        <v>0.29361565065375</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -7397,13 +7397,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.00157421525644398</v>
+        <v>1.57421525644398</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.00000762992240542321</v>
+        <v>0.00762992240542321</v>
       </c>
     </row>
     <row r="13">
@@ -7414,13 +7414,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000607914974399316</v>
+        <v>0.607914974399316</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0017394852597449</v>
+        <v>1.7394852597449</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7429,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.000125769294337682</v>
+        <v>0.125769294337682</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7450,16 +7450,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00069293293554285</v>
+        <v>0.69293293554285</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000179240825326823</v>
+        <v>0.179240825326823</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0369375254164228</v>
+        <v>36.9375254164228</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -7476,13 +7476,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00000343732214926915</v>
+        <v>0.00343732214926915</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00000131581845121259</v>
+        <v>0.00131581845121259</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00025473070686119</v>
+        <v>0.25473070686119</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7491,28 +7491,28 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.061028617233554</v>
+        <v>61.028617233554</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0000137961279840262</v>
+        <v>0.0137961279840262</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000862687078265905</v>
+        <v>0.862687078265905</v>
       </c>
       <c r="K14" t="n">
-        <v>0.000400617595229609</v>
+        <v>0.400617595229609</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.00002481828307723</v>
+        <v>0.02481828307723</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00312876837336636</v>
+        <v>3.12876837336636</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -7521,13 +7521,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.000810678041444548</v>
+        <v>0.810678041444548</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0000639526223436382</v>
+        <v>0.0639526223436382</v>
       </c>
     </row>
     <row r="15">
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000263181765784721</v>
+        <v>0.0263181765784721</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00101669000239466</v>
+        <v>1.01669000239467</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.000308864057076844</v>
+        <v>0.308864057076844</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -7597,37 +7597,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0132112254585925</v>
+        <v>13.2112254585925</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000259959763689013</v>
+        <v>0.259959763689013</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000139574063121164</v>
+        <v>0.139574063121164</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0000137939351384725</v>
+        <v>0.0137939351384725</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0000182178908028405</v>
+        <v>0.0182178908028405</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0000127348873698703</v>
+        <v>0.0127348873698703</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00000181271401354822</v>
+        <v>0.00181271401354822</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00000351721421186264</v>
+        <v>0.00351721421186264</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00000310713784133463</v>
+        <v>0.00310713784133463</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -7636,22 +7636,22 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.00003053602766799</v>
+        <v>0.03053602766799</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0000179870267795532</v>
+        <v>0.0179870267795532</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0000959464355563002</v>
+        <v>0.0959464355563002</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.00000752587800898562</v>
+        <v>0.00752587800898562</v>
       </c>
     </row>
     <row r="17">
@@ -7659,46 +7659,46 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00392104652839278</v>
+        <v>3.92104652839278</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00026172752936578</v>
+        <v>0.26172752936578</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0000456028075980013</v>
+        <v>0.0456028075980013</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000720884098902772</v>
+        <v>0.720884098902772</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00681595002614445</v>
+        <v>6.81595002614445</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.000747811493557561</v>
+        <v>0.747811493557561</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000365730046653464</v>
+        <v>0.365730046653464</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0000199398541490305</v>
+        <v>0.0199398541490305</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0000166205612756646</v>
+        <v>0.0166205612756646</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0000144171195837927</v>
+        <v>0.0144171195837927</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0000352512198657929</v>
+        <v>0.0352512198657929</v>
       </c>
       <c r="N17" t="n">
-        <v>0.00000996221229817932</v>
+        <v>0.00996221229817932</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00097950181058091</v>
+        <v>0.97950181058091</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.00134440089900979</v>
+        <v>1.34440089900979</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.00140883049069592</v>
+        <v>1.40883049069592</v>
       </c>
     </row>
     <row r="18">
@@ -7783,61 +7783,61 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.00219998476460011</v>
+        <v>2.19998476460011</v>
       </c>
       <c r="C19" t="n">
-        <v>0.000042917422263732</v>
+        <v>0.042917422263732</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000062199943918874</v>
+        <v>0.062199943918874</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000184110266375623</v>
+        <v>0.184110266375623</v>
       </c>
       <c r="F19" t="n">
-        <v>0.000188109697753346</v>
+        <v>0.188109697753346</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00000973707268488032</v>
+        <v>0.00973707268488032</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0000680427246853079</v>
+        <v>0.0680427246853079</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000050276274095634</v>
+        <v>0.050276274095634</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0000118650371795884</v>
+        <v>0.0118650371795884</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0000084137281146518</v>
+        <v>0.0084137281146518</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00000596570465536249</v>
+        <v>0.00596570465536249</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0000165217838562908</v>
+        <v>0.0165217838562908</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0000061834421161113</v>
+        <v>0.0061834421161113</v>
       </c>
       <c r="O19" t="n">
-        <v>0.000190850172924937</v>
+        <v>0.190850172924937</v>
       </c>
       <c r="P19" t="n">
-        <v>0.000315325248070562</v>
+        <v>0.315325248070562</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0000171616182848892</v>
+        <v>0.0171616182848892</v>
       </c>
       <c r="R19" t="n">
-        <v>0.000165417977840605</v>
+        <v>0.165417977840605</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.000143407859756477</v>
+        <v>0.143407859756477</v>
       </c>
     </row>
     <row r="20">
@@ -7854,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000436355367671068</v>
+        <v>0.436355367671068</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -7863,7 +7863,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0000531172237865952</v>
+        <v>0.0531172237865952</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -7878,13 +7878,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0000637459559239755</v>
+        <v>0.0637459559239755</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00221826624068908</v>
+        <v>2.21826624068908</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.000549724166685682</v>
+        <v>0.549724166685682</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -7989,37 +7989,37 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.536364438669262</v>
+        <v>0.457211558882527</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0371616718982588</v>
+        <v>0.0414785756177366</v>
       </c>
       <c r="H2" t="n">
-        <v>0.290827774864622</v>
+        <v>0.0330283129167675</v>
       </c>
       <c r="I2" t="n">
-        <v>0.219809462207033</v>
+        <v>0.0826081728348433</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0220821525286784</v>
+        <v>0.00334022183460139</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0266204840348819</v>
+        <v>0.00962183304594131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00869998595573696</v>
+        <v>0.00174489200314998</v>
       </c>
       <c r="M2" t="n">
-        <v>0.113311307492848</v>
+        <v>0.317296147258515</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0274819649604947</v>
+        <v>0.00398832457862852</v>
       </c>
       <c r="O2" t="n">
-        <v>0.592809998669921</v>
+        <v>0.0503276707765687</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.575251911761256</v>
+        <v>4.43586445040788</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.288064252270205</v>
+        <v>0.207043899688053</v>
       </c>
     </row>
     <row r="3">
@@ -8042,28 +8042,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>8.13795195943395</v>
+        <v>32.0624571255443</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0860681567012282</v>
+        <v>1.61239871562003</v>
       </c>
       <c r="E3" t="n">
-        <v>0.100009070998194</v>
+        <v>0.335875478585729</v>
       </c>
       <c r="F3" t="n">
-        <v>1.22690359797046</v>
+        <v>2.07025002590268</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0526782384660448</v>
+        <v>0.0235702090235599</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0230156558195053</v>
+        <v>0.034078593879897</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0863230012922025</v>
+        <v>0.0288735060538609</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -8090,13 +8090,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.248408201890903</v>
+        <v>7.54688630173108</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0432131059870787</v>
+        <v>0.122368668513982</v>
       </c>
     </row>
     <row r="4">
@@ -8104,7 +8104,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.33561751329159</v>
+        <v>0.0705823889526944</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8113,7 +8113,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.624208663604518</v>
+        <v>0.111902233703522</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -8122,43 +8122,43 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0335823770221036</v>
+        <v>0.000802072601735164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0252707921245865</v>
+        <v>0.00199731804745815</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000823960915249193</v>
+        <v>0.0000262115229325217</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00534427708709556</v>
+        <v>0.000225419097219687</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0166998203202595</v>
+        <v>0.00983456340428214</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.350283471229924</v>
+        <v>0.00625406937169968</v>
       </c>
       <c r="P4" t="n">
-        <v>5.76578988817137</v>
+        <v>0.191905043998164</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.06560960531627</v>
+        <v>1.72810473772281</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0986340878228346</v>
+        <v>0.0149091142440183</v>
       </c>
     </row>
     <row r="5">
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95732215525195</v>
+        <v>17.7061966263724</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -8228,16 +8228,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3.21563654557648</v>
+        <v>7.50820768241868</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0274434645103502</v>
+        <v>0.304688820463728</v>
       </c>
       <c r="E6" t="n">
-        <v>0.736762732105117</v>
+        <v>1.46640588950976</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -8246,28 +8246,28 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.376429912371945</v>
+        <v>0.0998168724155287</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0362542802709645</v>
+        <v>0.0128044967530124</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0180688259511375</v>
+        <v>0.0152489915876784</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0274670985173981</v>
+        <v>0.0128626990109807</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0166019002650767</v>
+        <v>0.108547211110764</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0200961868773617</v>
+        <v>0.00680966418228389</v>
       </c>
       <c r="O6" t="n">
-        <v>0.454810642862659</v>
+        <v>0.0901552975928012</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -8276,13 +8276,13 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.276955183879302</v>
+        <v>4.98653665368679</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.243741339387792</v>
+        <v>0.409045469000779</v>
       </c>
     </row>
     <row r="7">
@@ -8293,58 +8293,58 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.171964316667722</v>
+        <v>0.0391046198881318</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0221382522688078</v>
+        <v>0.0943111420831413</v>
       </c>
       <c r="E7" t="n">
-        <v>1.74056722922646</v>
+        <v>1.32928908337029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.70174462432305</v>
+        <v>0.269265792113766</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.35890474040493</v>
+        <v>0.443505794607886</v>
       </c>
       <c r="I7" t="n">
-        <v>13.7846533198856</v>
+        <v>4.64134542403813</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0210933994303793</v>
+        <v>0.00285859014601991</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0352411071031727</v>
+        <v>0.0114120278485639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0290828101948921</v>
+        <v>0.00522586011069265</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0902377817625108</v>
+        <v>0.226386939923468</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0712813466162831</v>
+        <v>0.00926808523904893</v>
       </c>
       <c r="O7" t="n">
-        <v>13.2485253887985</v>
+        <v>1.00769769194305</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0646226067280697</v>
+        <v>0.0419632100341517</v>
       </c>
       <c r="R7" t="n">
-        <v>2.07366621920218</v>
+        <v>14.326181840547</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>30.6671552129104</v>
+        <v>19.7477660453</v>
       </c>
     </row>
     <row r="8">
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0791299842459395</v>
+        <v>0.593947138704655</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -8400,7 +8400,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.252772195287386</v>
+        <v>17.1632285702182</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -8423,16 +8423,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.344621901085882</v>
+        <v>0.781670039864177</v>
       </c>
       <c r="F9" t="n">
-        <v>0.524227737519923</v>
+        <v>0.597412138231366</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.112599734721171</v>
+        <v>0.0340260271913723</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -8447,13 +8447,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00371206027374637</v>
+        <v>0.0276585835064372</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4462957889937</v>
+        <v>0.100817858344807</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -8462,13 +8462,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33841091399966</v>
+        <v>27.4620550102032</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9624106670477</v>
+        <v>1.84058919017657</v>
       </c>
     </row>
     <row r="10">
@@ -8479,13 +8479,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00569613384736031</v>
+        <v>0.00955794661689064</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.26970580781918</v>
+        <v>7.15527658802399</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -8494,28 +8494,28 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82289510379918</v>
+        <v>2.11939226620397</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0195666238234987</v>
+        <v>0.0486136939997024</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.563443923743486</v>
+        <v>1.34635213551718</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0642889671390799</v>
+        <v>1.19012914598593</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.682069156468661</v>
+        <v>0.382812241224775</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -8524,13 +8524,13 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.83788005036591</v>
+        <v>195.649024949372</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0258723732474805</v>
+        <v>0.12293496855518</v>
       </c>
     </row>
     <row r="11">
@@ -8541,13 +8541,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000392836817059332</v>
+        <v>0.000275859938185305</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000424626671506852</v>
+        <v>0.00558616374825243</v>
       </c>
       <c r="E11" t="n">
-        <v>0.436881731202637</v>
+        <v>1.03033686912211</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -8556,10 +8556,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.354041661023876</v>
+        <v>0.111240520073224</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0130001975234093</v>
+        <v>0.0135171369710799</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -8571,13 +8571,13 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.157063768513144</v>
+        <v>1.21681818733538</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.326206987876316</v>
+        <v>0.0766200978309685</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.61833461872334</v>
+        <v>55.8603271478179</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.00610393792433857</v>
+        <v>0.0121378372801534</v>
       </c>
     </row>
     <row r="12">
@@ -8603,13 +8603,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00913345599662946</v>
+        <v>0.0115585527697648</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.162470876744435</v>
+        <v>0.690530313858208</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -8618,28 +8618,28 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.714668101856008</v>
+        <v>0.404673632455422</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00291841168892862</v>
+        <v>0.00546856260074894</v>
       </c>
       <c r="J12" t="n">
-        <v>0.80665773602896</v>
+        <v>0.60837758933332</v>
       </c>
       <c r="K12" t="n">
-        <v>0.276687517999861</v>
+        <v>0.498633480777381</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.078923564477303</v>
+        <v>1.10191536405091</v>
       </c>
       <c r="N12" t="n">
-        <v>1.03126073514256</v>
+        <v>0.746210223974924</v>
       </c>
       <c r="O12" t="n">
-        <v>0.29361565065375</v>
+        <v>0.124285513653385</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -8648,13 +8648,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57421525644398</v>
+        <v>60.5249322954664</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.00762992240542321</v>
+        <v>0.0273428130037447</v>
       </c>
     </row>
     <row r="13">
@@ -8665,13 +8665,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.607914974399316</v>
+        <v>0.0551022855982975</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7394852597449</v>
+        <v>0.52952495295876</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -8680,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.125769294337682</v>
+        <v>0.00510074469270185</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -8701,16 +8701,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.69293293554285</v>
+        <v>0.0210083027483008</v>
       </c>
       <c r="P13" t="n">
-        <v>0.179240825326823</v>
+        <v>0.0101302747998162</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>36.9375254164228</v>
+        <v>101.717679781088</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -8727,13 +8727,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00343732214926915</v>
+        <v>0.00601167983510821</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00131581845121259</v>
+        <v>0.043112332531776</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25473070686119</v>
+        <v>1.49622122981793</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -8742,28 +8742,28 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>61.028617233554</v>
+        <v>47.7574716592236</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0137961279840262</v>
+        <v>0.0357265544486431</v>
       </c>
       <c r="J14" t="n">
-        <v>0.862687078265905</v>
+        <v>0.899175541051185</v>
       </c>
       <c r="K14" t="n">
-        <v>0.400617595229609</v>
+        <v>0.99776709034696</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02481828307723</v>
+        <v>0.47887323943662</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.12876837336636</v>
+        <v>1.83029886636895</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -8772,13 +8772,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.810678041444548</v>
+        <v>43.0750601167984</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0639526223436382</v>
+        <v>0.316729646169701</v>
       </c>
     </row>
     <row r="15">
@@ -8795,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0263181765784721</v>
+        <v>0.264254085588375</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01669000239467</v>
+        <v>1.36002769382817</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.308864057076844</v>
+        <v>28.0540945730138</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -8848,37 +8848,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>13.2112254585925</v>
+        <v>83.4770830051977</v>
       </c>
       <c r="C16" t="n">
-        <v>0.259959763689013</v>
+        <v>0.416916049771618</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.139574063121164</v>
+        <v>0.751771932587809</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0137939351384725</v>
+        <v>0.0373287131831785</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0182178908028405</v>
+        <v>0.0130729248700583</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0127348873698703</v>
+        <v>0.030240982831942</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00181271401354822</v>
+        <v>0.00173255630808001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00351721421186264</v>
+        <v>0.0080327610647346</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00310713784133463</v>
+        <v>0.00393762797290912</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -8887,22 +8887,22 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.03053602766799</v>
+        <v>0.0163805323673019</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0179870267795532</v>
+        <v>0.0823751771932588</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0959464355563002</v>
+        <v>4.67490943455662</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.00752587800898562</v>
+        <v>0.0341786108048512</v>
       </c>
     </row>
     <row r="17">
@@ -8910,46 +8910,46 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3.92104652839278</v>
+        <v>5.40989923413097</v>
       </c>
       <c r="C17" t="n">
-        <v>0.26172752936578</v>
+        <v>0.091654734928316</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0456028075980013</v>
+        <v>0.299176187295092</v>
       </c>
       <c r="E17" t="n">
-        <v>0.720884098902772</v>
+        <v>0.847832092102381</v>
       </c>
       <c r="F17" t="n">
-        <v>6.81595002614445</v>
+        <v>4.02758074971303</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.747811493557561</v>
+        <v>0.117173614221678</v>
       </c>
       <c r="I17" t="n">
-        <v>0.365730046653464</v>
+        <v>0.189637601649056</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0199398541490305</v>
+        <v>0.00416143449393105</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0166205612756646</v>
+        <v>0.00828847696725109</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0144171195837927</v>
+        <v>0.00398947439087604</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0352512198657929</v>
+        <v>0.136192401619562</v>
       </c>
       <c r="N17" t="n">
-        <v>0.00996221229817932</v>
+        <v>0.00199473719543802</v>
       </c>
       <c r="O17" t="n">
-        <v>0.97950181058091</v>
+        <v>0.114731780758297</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -8958,13 +8958,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34440089900979</v>
+        <v>14.3032974519089</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.40883049069592</v>
+        <v>1.39707266126006</v>
       </c>
     </row>
     <row r="18">
@@ -9034,61 +9034,61 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2.19998476460011</v>
+        <v>26.2936962101947</v>
       </c>
       <c r="C19" t="n">
-        <v>0.042917422263732</v>
+        <v>0.130191885559843</v>
       </c>
       <c r="D19" t="n">
-        <v>0.062199943918874</v>
+        <v>3.53484375782045</v>
       </c>
       <c r="E19" t="n">
-        <v>0.184110266375623</v>
+        <v>1.87571650225348</v>
       </c>
       <c r="F19" t="n">
-        <v>0.188109697753346</v>
+        <v>0.962883693659983</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00973707268488032</v>
+        <v>0.129893963624923</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0680427246853079</v>
+        <v>0.0923557998250602</v>
       </c>
       <c r="I19" t="n">
-        <v>0.050276274095634</v>
+        <v>0.225824826669018</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0118650371795884</v>
+        <v>0.0214503793142075</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0084137281146518</v>
+        <v>0.036346476060185</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00596570465536249</v>
+        <v>0.0143002528761384</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0165217838562908</v>
+        <v>0.552943111210683</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0061834421161113</v>
+        <v>0.0107251896571038</v>
       </c>
       <c r="O19" t="n">
-        <v>0.190850172924937</v>
+        <v>0.193649257697707</v>
       </c>
       <c r="P19" t="n">
-        <v>0.315325248070562</v>
+        <v>0.596439713708937</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0171616182848892</v>
+        <v>0.148663045524855</v>
       </c>
       <c r="R19" t="n">
-        <v>0.165417977840605</v>
+        <v>15.2452612537032</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.143407859756477</v>
+        <v>1.23190720089234</v>
       </c>
     </row>
     <row r="20">
@@ -9105,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.436355367671068</v>
+        <v>0.517516827880569</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -9114,7 +9114,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0531172237865952</v>
+        <v>0.00839291464596553</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -9129,13 +9129,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0637459559239755</v>
+        <v>0.248353974296526</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.21826624068908</v>
+        <v>0.262018471695329</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -9144,7 +9144,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.549724166685682</v>
+        <v>5.8978259749957</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
